--- a/public/sap-reporting/expansion-150-downloads/EXT-CO28-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO28-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3a8d594d3a65433d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R2d25cf2db09d4578"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rcdb123bb36994775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R27e851978592467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R4c035f45574543fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rf71e434662cb493d"/>
   </x:sheets>
 </x:workbook>
 </file>
